--- a/5P06 Design History File (DHF) Team 9/5P06 Design History File (DHF) Team 9/4-Design Outputs/Risk Management/Selfie_Dental_Assistant_Appication_FMEA.xlsx
+++ b/5P06 Design History File (DHF) Team 9/5P06 Design History File (DHF) Team 9/4-Design Outputs/Risk Management/Selfie_Dental_Assistant_Appication_FMEA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruidi Liu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\McMaster_University\6thYear_2025-2026\SFWRBME_5P06\SFWRBME-5P06\5P06 Design History File (DHF) Team 9\5P06 Design History File (DHF) Team 9\4-Design Outputs\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE8A4E7-AC08-49CA-A6E4-7C95CFBC13CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBE0C87-E171-4D74-851F-B6893BECB3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,6 +1554,12 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1603,12 +1609,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2022,7 +2022,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IZ27"/>
+  <dimension ref="A1:KJ27"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -2044,11 +2044,13 @@
     <col min="19" max="19" width="10.6640625" customWidth="1"/>
     <col min="20" max="22" width="6.44140625" customWidth="1"/>
     <col min="23" max="23" width="8.109375" customWidth="1"/>
-    <col min="24" max="24" width="2.6640625" customWidth="1"/>
+    <col min="27" max="296" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:260" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:260" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:81" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="CC1" s="2"/>
+    </row>
+    <row r="2" spans="1:81" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -2063,261 +2065,28 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2"/>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
-      <c r="BR2" s="2"/>
-      <c r="BS2" s="2"/>
-      <c r="BT2" s="2"/>
-      <c r="BU2" s="2"/>
-      <c r="BV2" s="2"/>
-      <c r="BW2" s="2"/>
-      <c r="BX2" s="2"/>
-      <c r="BY2" s="2"/>
-      <c r="BZ2" s="2"/>
-      <c r="CA2" s="2"/>
-      <c r="CB2" s="2"/>
-      <c r="CC2" s="2"/>
-      <c r="CD2" s="2"/>
-      <c r="CE2" s="2"/>
-      <c r="CF2" s="2"/>
-      <c r="CG2" s="2"/>
-      <c r="CH2" s="2"/>
-      <c r="CI2" s="2"/>
-      <c r="CJ2" s="2"/>
-      <c r="CK2" s="2"/>
-      <c r="CL2" s="2"/>
-      <c r="CM2" s="2"/>
-      <c r="CN2" s="2"/>
-      <c r="CO2" s="2"/>
-      <c r="CP2" s="2"/>
-      <c r="CQ2" s="2"/>
-      <c r="CR2" s="2"/>
-      <c r="CS2" s="2"/>
-      <c r="CT2" s="2"/>
-      <c r="CU2" s="2"/>
-      <c r="CV2" s="2"/>
-      <c r="CW2" s="2"/>
-      <c r="CX2" s="2"/>
-      <c r="CY2" s="2"/>
-      <c r="CZ2" s="2"/>
-      <c r="DA2" s="2"/>
-      <c r="DB2" s="2"/>
-      <c r="DC2" s="2"/>
-      <c r="DD2" s="2"/>
-      <c r="DE2" s="2"/>
-      <c r="DF2" s="2"/>
-      <c r="DG2" s="2"/>
-      <c r="DH2" s="2"/>
-      <c r="DI2" s="2"/>
-      <c r="DJ2" s="2"/>
-      <c r="DK2" s="2"/>
-      <c r="DL2" s="2"/>
-      <c r="DM2" s="2"/>
-      <c r="DN2" s="2"/>
-      <c r="DO2" s="2"/>
-      <c r="DP2" s="2"/>
-      <c r="DQ2" s="2"/>
-      <c r="DR2" s="2"/>
-      <c r="DS2" s="2"/>
-      <c r="DT2" s="2"/>
-      <c r="DU2" s="2"/>
-      <c r="DV2" s="2"/>
-      <c r="DW2" s="2"/>
-      <c r="DX2" s="2"/>
-      <c r="DY2" s="2"/>
-      <c r="DZ2" s="2"/>
-      <c r="EA2" s="2"/>
-      <c r="EB2" s="2"/>
-      <c r="EC2" s="2"/>
-      <c r="ED2" s="2"/>
-      <c r="EE2" s="2"/>
-      <c r="EF2" s="2"/>
-      <c r="EG2" s="2"/>
-      <c r="EH2" s="2"/>
-      <c r="EI2" s="2"/>
-      <c r="EJ2" s="2"/>
-      <c r="EK2" s="2"/>
-      <c r="EL2" s="2"/>
-      <c r="EM2" s="2"/>
-      <c r="EN2" s="2"/>
-      <c r="EO2" s="2"/>
-      <c r="EP2" s="2"/>
-      <c r="EQ2" s="2"/>
-      <c r="ER2" s="2"/>
-      <c r="ES2" s="2"/>
-      <c r="ET2" s="2"/>
-      <c r="EU2" s="2"/>
-      <c r="EV2" s="2"/>
-      <c r="EW2" s="2"/>
-      <c r="EX2" s="2"/>
-      <c r="EY2" s="2"/>
-      <c r="EZ2" s="2"/>
-      <c r="FA2" s="2"/>
-      <c r="FB2" s="2"/>
-      <c r="FC2" s="2"/>
-      <c r="FD2" s="2"/>
-      <c r="FE2" s="2"/>
-      <c r="FF2" s="2"/>
-      <c r="FG2" s="2"/>
-      <c r="FH2" s="2"/>
-      <c r="FI2" s="2"/>
-      <c r="FJ2" s="2"/>
-      <c r="FK2" s="2"/>
-      <c r="FL2" s="2"/>
-      <c r="FM2" s="2"/>
-      <c r="FN2" s="2"/>
-      <c r="FO2" s="2"/>
-      <c r="FP2" s="2"/>
-      <c r="FQ2" s="2"/>
-      <c r="FR2" s="2"/>
-      <c r="FS2" s="2"/>
-      <c r="FT2" s="2"/>
-      <c r="FU2" s="2"/>
-      <c r="FV2" s="2"/>
-      <c r="FW2" s="2"/>
-      <c r="FX2" s="2"/>
-      <c r="FY2" s="2"/>
-      <c r="FZ2" s="2"/>
-      <c r="GA2" s="2"/>
-      <c r="GB2" s="2"/>
-      <c r="GC2" s="2"/>
-      <c r="GD2" s="2"/>
-      <c r="GE2" s="2"/>
-      <c r="GF2" s="2"/>
-      <c r="GG2" s="2"/>
-      <c r="GH2" s="2"/>
-      <c r="GI2" s="2"/>
-      <c r="GJ2" s="2"/>
-      <c r="GK2" s="2"/>
-      <c r="GL2" s="2"/>
-      <c r="GM2" s="2"/>
-      <c r="GN2" s="2"/>
-      <c r="GO2" s="2"/>
-      <c r="GP2" s="2"/>
-      <c r="GQ2" s="2"/>
-      <c r="GR2" s="2"/>
-      <c r="GS2" s="2"/>
-      <c r="GT2" s="2"/>
-      <c r="GU2" s="2"/>
-      <c r="GV2" s="2"/>
-      <c r="GW2" s="2"/>
-      <c r="GX2" s="2"/>
-      <c r="GY2" s="2"/>
-      <c r="GZ2" s="2"/>
-      <c r="HA2" s="2"/>
-      <c r="HB2" s="2"/>
-      <c r="HC2" s="2"/>
-      <c r="HD2" s="2"/>
-      <c r="HE2" s="2"/>
-      <c r="HF2" s="2"/>
-      <c r="HG2" s="2"/>
-      <c r="HH2" s="2"/>
-      <c r="HI2" s="2"/>
-      <c r="HJ2" s="2"/>
-      <c r="HK2" s="2"/>
-      <c r="HL2" s="2"/>
-      <c r="HM2" s="2"/>
-      <c r="HN2" s="2"/>
-      <c r="HO2" s="2"/>
-      <c r="HP2" s="2"/>
-      <c r="HQ2" s="2"/>
-      <c r="HR2" s="2"/>
-      <c r="HS2" s="2"/>
-      <c r="HT2" s="2"/>
-      <c r="HU2" s="2"/>
-      <c r="HV2" s="2"/>
-      <c r="HW2" s="2"/>
-      <c r="HX2" s="2"/>
-      <c r="HY2" s="2"/>
-      <c r="HZ2" s="2"/>
-      <c r="IA2" s="2"/>
-      <c r="IB2" s="2"/>
-      <c r="IC2" s="2"/>
-      <c r="ID2" s="2"/>
-      <c r="IE2" s="2"/>
-      <c r="IF2" s="2"/>
-      <c r="IG2" s="2"/>
-      <c r="IH2" s="2"/>
-      <c r="II2" s="2"/>
-      <c r="IJ2" s="2"/>
-      <c r="IK2" s="2"/>
-      <c r="IL2" s="2"/>
-      <c r="IM2" s="2"/>
-      <c r="IN2" s="2"/>
-      <c r="IO2" s="2"/>
-      <c r="IP2" s="2"/>
-      <c r="IQ2" s="2"/>
-      <c r="IR2" s="2"/>
-      <c r="IS2" s="2"/>
-      <c r="IT2" s="2"/>
-      <c r="IU2" s="2"/>
-      <c r="IV2" s="2"/>
-    </row>
-    <row r="3" spans="1:260" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="64" t="s">
+    </row>
+    <row r="3" spans="1:81" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="66"/>
-      <c r="J3" s="68" t="s">
+      <c r="I3" s="68"/>
+      <c r="J3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="66"/>
-      <c r="L3" s="67" t="s">
+      <c r="K3" s="68"/>
+      <c r="L3" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="66"/>
+      <c r="M3" s="68"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2327,261 +2096,24 @@
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
-      <c r="AP3" s="6"/>
-      <c r="AQ3" s="6"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
-      <c r="AT3" s="6"/>
-      <c r="AU3" s="6"/>
-      <c r="AV3" s="6"/>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="6"/>
-      <c r="AY3" s="6"/>
-      <c r="AZ3" s="6"/>
-      <c r="BA3" s="6"/>
-      <c r="BB3" s="6"/>
-      <c r="BC3" s="6"/>
-      <c r="BD3" s="6"/>
-      <c r="BE3" s="6"/>
-      <c r="BF3" s="6"/>
-      <c r="BG3" s="6"/>
-      <c r="BH3" s="6"/>
-      <c r="BI3" s="6"/>
-      <c r="BJ3" s="6"/>
-      <c r="BK3" s="6"/>
-      <c r="BL3" s="6"/>
-      <c r="BM3" s="6"/>
-      <c r="BN3" s="6"/>
-      <c r="BO3" s="6"/>
-      <c r="BP3" s="6"/>
-      <c r="BQ3" s="6"/>
-      <c r="BR3" s="6"/>
-      <c r="BS3" s="6"/>
-      <c r="BT3" s="6"/>
-      <c r="BU3" s="6"/>
-      <c r="BV3" s="6"/>
-      <c r="BW3" s="6"/>
-      <c r="BX3" s="6"/>
-      <c r="BY3" s="6"/>
-      <c r="BZ3" s="6"/>
-      <c r="CA3" s="6"/>
-      <c r="CB3" s="6"/>
-      <c r="CC3" s="6"/>
-      <c r="CD3" s="6"/>
-      <c r="CE3" s="6"/>
-      <c r="CF3" s="6"/>
-      <c r="CG3" s="6"/>
-      <c r="CH3" s="6"/>
-      <c r="CI3" s="6"/>
-      <c r="CJ3" s="6"/>
-      <c r="CK3" s="6"/>
-      <c r="CL3" s="6"/>
-      <c r="CM3" s="6"/>
-      <c r="CN3" s="6"/>
-      <c r="CO3" s="6"/>
-      <c r="CP3" s="6"/>
-      <c r="CQ3" s="6"/>
-      <c r="CR3" s="6"/>
-      <c r="CS3" s="6"/>
-      <c r="CT3" s="6"/>
-      <c r="CU3" s="6"/>
-      <c r="CV3" s="6"/>
-      <c r="CW3" s="6"/>
-      <c r="CX3" s="6"/>
-      <c r="CY3" s="6"/>
-      <c r="CZ3" s="6"/>
-      <c r="DA3" s="6"/>
-      <c r="DB3" s="6"/>
-      <c r="DC3" s="6"/>
-      <c r="DD3" s="6"/>
-      <c r="DE3" s="6"/>
-      <c r="DF3" s="6"/>
-      <c r="DG3" s="6"/>
-      <c r="DH3" s="6"/>
-      <c r="DI3" s="6"/>
-      <c r="DJ3" s="6"/>
-      <c r="DK3" s="6"/>
-      <c r="DL3" s="6"/>
-      <c r="DM3" s="6"/>
-      <c r="DN3" s="6"/>
-      <c r="DO3" s="6"/>
-      <c r="DP3" s="6"/>
-      <c r="DQ3" s="6"/>
-      <c r="DR3" s="6"/>
-      <c r="DS3" s="6"/>
-      <c r="DT3" s="6"/>
-      <c r="DU3" s="6"/>
-      <c r="DV3" s="6"/>
-      <c r="DW3" s="6"/>
-      <c r="DX3" s="6"/>
-      <c r="DY3" s="6"/>
-      <c r="DZ3" s="6"/>
-      <c r="EA3" s="6"/>
-      <c r="EB3" s="6"/>
-      <c r="EC3" s="6"/>
-      <c r="ED3" s="6"/>
-      <c r="EE3" s="6"/>
-      <c r="EF3" s="6"/>
-      <c r="EG3" s="6"/>
-      <c r="EH3" s="6"/>
-      <c r="EI3" s="6"/>
-      <c r="EJ3" s="6"/>
-      <c r="EK3" s="6"/>
-      <c r="EL3" s="6"/>
-      <c r="EM3" s="6"/>
-      <c r="EN3" s="6"/>
-      <c r="EO3" s="6"/>
-      <c r="EP3" s="6"/>
-      <c r="EQ3" s="6"/>
-      <c r="ER3" s="6"/>
-      <c r="ES3" s="6"/>
-      <c r="ET3" s="6"/>
-      <c r="EU3" s="6"/>
-      <c r="EV3" s="6"/>
-      <c r="EW3" s="6"/>
-      <c r="EX3" s="6"/>
-      <c r="EY3" s="6"/>
-      <c r="EZ3" s="6"/>
-      <c r="FA3" s="6"/>
-      <c r="FB3" s="6"/>
-      <c r="FC3" s="6"/>
-      <c r="FD3" s="6"/>
-      <c r="FE3" s="6"/>
-      <c r="FF3" s="6"/>
-      <c r="FG3" s="6"/>
-      <c r="FH3" s="6"/>
-      <c r="FI3" s="6"/>
-      <c r="FJ3" s="6"/>
-      <c r="FK3" s="6"/>
-      <c r="FL3" s="6"/>
-      <c r="FM3" s="6"/>
-      <c r="FN3" s="6"/>
-      <c r="FO3" s="6"/>
-      <c r="FP3" s="6"/>
-      <c r="FQ3" s="6"/>
-      <c r="FR3" s="6"/>
-      <c r="FS3" s="6"/>
-      <c r="FT3" s="6"/>
-      <c r="FU3" s="6"/>
-      <c r="FV3" s="6"/>
-      <c r="FW3" s="6"/>
-      <c r="FX3" s="6"/>
-      <c r="FY3" s="6"/>
-      <c r="FZ3" s="6"/>
-      <c r="GA3" s="6"/>
-      <c r="GB3" s="6"/>
-      <c r="GC3" s="6"/>
-      <c r="GD3" s="6"/>
-      <c r="GE3" s="6"/>
-      <c r="GF3" s="6"/>
-      <c r="GG3" s="6"/>
-      <c r="GH3" s="6"/>
-      <c r="GI3" s="6"/>
-      <c r="GJ3" s="6"/>
-      <c r="GK3" s="6"/>
-      <c r="GL3" s="6"/>
-      <c r="GM3" s="6"/>
-      <c r="GN3" s="6"/>
-      <c r="GO3" s="6"/>
-      <c r="GP3" s="6"/>
-      <c r="GQ3" s="6"/>
-      <c r="GR3" s="6"/>
-      <c r="GS3" s="6"/>
-      <c r="GT3" s="6"/>
-      <c r="GU3" s="6"/>
-      <c r="GV3" s="6"/>
-      <c r="GW3" s="6"/>
-      <c r="GX3" s="6"/>
-      <c r="GY3" s="6"/>
-      <c r="GZ3" s="6"/>
-      <c r="HA3" s="6"/>
-      <c r="HB3" s="6"/>
-      <c r="HC3" s="6"/>
-      <c r="HD3" s="6"/>
-      <c r="HE3" s="6"/>
-      <c r="HF3" s="6"/>
-      <c r="HG3" s="6"/>
-      <c r="HH3" s="6"/>
-      <c r="HI3" s="6"/>
-      <c r="HJ3" s="6"/>
-      <c r="HK3" s="6"/>
-      <c r="HL3" s="6"/>
-      <c r="HM3" s="6"/>
-      <c r="HN3" s="6"/>
-      <c r="HO3" s="6"/>
-      <c r="HP3" s="6"/>
-      <c r="HQ3" s="6"/>
-      <c r="HR3" s="6"/>
-      <c r="HS3" s="6"/>
-      <c r="HT3" s="6"/>
-      <c r="HU3" s="6"/>
-      <c r="HV3" s="6"/>
-      <c r="HW3" s="6"/>
-      <c r="HX3" s="6"/>
-      <c r="HY3" s="6"/>
-      <c r="HZ3" s="6"/>
-      <c r="IA3" s="6"/>
-      <c r="IB3" s="6"/>
-      <c r="IC3" s="6"/>
-      <c r="ID3" s="6"/>
-      <c r="IE3" s="6"/>
-      <c r="IF3" s="6"/>
-      <c r="IG3" s="6"/>
-      <c r="IH3" s="6"/>
-      <c r="II3" s="6"/>
-      <c r="IJ3" s="6"/>
-      <c r="IK3" s="6"/>
-      <c r="IL3" s="6"/>
-      <c r="IM3" s="6"/>
-      <c r="IN3" s="6"/>
-      <c r="IO3" s="6"/>
-      <c r="IP3" s="6"/>
-      <c r="IQ3" s="6"/>
-      <c r="IR3" s="6"/>
-      <c r="IS3" s="6"/>
-      <c r="IT3" s="6"/>
-      <c r="IU3" s="6"/>
-      <c r="IV3" s="6"/>
-      <c r="IW3" s="6"/>
-      <c r="IX3" s="6"/>
-      <c r="IY3" s="6"/>
-      <c r="IZ3" s="6"/>
-    </row>
-    <row r="4" spans="1:260" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="69" t="s">
+    </row>
+    <row r="4" spans="1:81" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="73" t="s">
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="M4" s="71"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2592,265 +2124,28 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="6"/>
-      <c r="AP4" s="6"/>
-      <c r="AQ4" s="6"/>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="6"/>
-      <c r="AT4" s="6"/>
-      <c r="AU4" s="6"/>
-      <c r="AV4" s="6"/>
-      <c r="AW4" s="6"/>
-      <c r="AX4" s="6"/>
-      <c r="AY4" s="6"/>
-      <c r="AZ4" s="6"/>
-      <c r="BA4" s="6"/>
-      <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
-      <c r="BD4" s="6"/>
-      <c r="BE4" s="6"/>
-      <c r="BF4" s="6"/>
-      <c r="BG4" s="6"/>
-      <c r="BH4" s="6"/>
-      <c r="BI4" s="6"/>
-      <c r="BJ4" s="6"/>
-      <c r="BK4" s="6"/>
-      <c r="BL4" s="6"/>
-      <c r="BM4" s="6"/>
-      <c r="BN4" s="6"/>
-      <c r="BO4" s="6"/>
-      <c r="BP4" s="6"/>
-      <c r="BQ4" s="6"/>
-      <c r="BR4" s="6"/>
-      <c r="BS4" s="6"/>
-      <c r="BT4" s="6"/>
-      <c r="BU4" s="6"/>
-      <c r="BV4" s="6"/>
-      <c r="BW4" s="6"/>
-      <c r="BX4" s="6"/>
-      <c r="BY4" s="6"/>
-      <c r="BZ4" s="6"/>
-      <c r="CA4" s="6"/>
-      <c r="CB4" s="6"/>
-      <c r="CC4" s="6"/>
-      <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
-      <c r="CF4" s="6"/>
-      <c r="CG4" s="6"/>
-      <c r="CH4" s="6"/>
-      <c r="CI4" s="6"/>
-      <c r="CJ4" s="6"/>
-      <c r="CK4" s="6"/>
-      <c r="CL4" s="6"/>
-      <c r="CM4" s="6"/>
-      <c r="CN4" s="6"/>
-      <c r="CO4" s="6"/>
-      <c r="CP4" s="6"/>
-      <c r="CQ4" s="6"/>
-      <c r="CR4" s="6"/>
-      <c r="CS4" s="6"/>
-      <c r="CT4" s="6"/>
-      <c r="CU4" s="6"/>
-      <c r="CV4" s="6"/>
-      <c r="CW4" s="6"/>
-      <c r="CX4" s="6"/>
-      <c r="CY4" s="6"/>
-      <c r="CZ4" s="6"/>
-      <c r="DA4" s="6"/>
-      <c r="DB4" s="6"/>
-      <c r="DC4" s="6"/>
-      <c r="DD4" s="6"/>
-      <c r="DE4" s="6"/>
-      <c r="DF4" s="6"/>
-      <c r="DG4" s="6"/>
-      <c r="DH4" s="6"/>
-      <c r="DI4" s="6"/>
-      <c r="DJ4" s="6"/>
-      <c r="DK4" s="6"/>
-      <c r="DL4" s="6"/>
-      <c r="DM4" s="6"/>
-      <c r="DN4" s="6"/>
-      <c r="DO4" s="6"/>
-      <c r="DP4" s="6"/>
-      <c r="DQ4" s="6"/>
-      <c r="DR4" s="6"/>
-      <c r="DS4" s="6"/>
-      <c r="DT4" s="6"/>
-      <c r="DU4" s="6"/>
-      <c r="DV4" s="6"/>
-      <c r="DW4" s="6"/>
-      <c r="DX4" s="6"/>
-      <c r="DY4" s="6"/>
-      <c r="DZ4" s="6"/>
-      <c r="EA4" s="6"/>
-      <c r="EB4" s="6"/>
-      <c r="EC4" s="6"/>
-      <c r="ED4" s="6"/>
-      <c r="EE4" s="6"/>
-      <c r="EF4" s="6"/>
-      <c r="EG4" s="6"/>
-      <c r="EH4" s="6"/>
-      <c r="EI4" s="6"/>
-      <c r="EJ4" s="6"/>
-      <c r="EK4" s="6"/>
-      <c r="EL4" s="6"/>
-      <c r="EM4" s="6"/>
-      <c r="EN4" s="6"/>
-      <c r="EO4" s="6"/>
-      <c r="EP4" s="6"/>
-      <c r="EQ4" s="6"/>
-      <c r="ER4" s="6"/>
-      <c r="ES4" s="6"/>
-      <c r="ET4" s="6"/>
-      <c r="EU4" s="6"/>
-      <c r="EV4" s="6"/>
-      <c r="EW4" s="6"/>
-      <c r="EX4" s="6"/>
-      <c r="EY4" s="6"/>
-      <c r="EZ4" s="6"/>
-      <c r="FA4" s="6"/>
-      <c r="FB4" s="6"/>
-      <c r="FC4" s="6"/>
-      <c r="FD4" s="6"/>
-      <c r="FE4" s="6"/>
-      <c r="FF4" s="6"/>
-      <c r="FG4" s="6"/>
-      <c r="FH4" s="6"/>
-      <c r="FI4" s="6"/>
-      <c r="FJ4" s="6"/>
-      <c r="FK4" s="6"/>
-      <c r="FL4" s="6"/>
-      <c r="FM4" s="6"/>
-      <c r="FN4" s="6"/>
-      <c r="FO4" s="6"/>
-      <c r="FP4" s="6"/>
-      <c r="FQ4" s="6"/>
-      <c r="FR4" s="6"/>
-      <c r="FS4" s="6"/>
-      <c r="FT4" s="6"/>
-      <c r="FU4" s="6"/>
-      <c r="FV4" s="6"/>
-      <c r="FW4" s="6"/>
-      <c r="FX4" s="6"/>
-      <c r="FY4" s="6"/>
-      <c r="FZ4" s="6"/>
-      <c r="GA4" s="6"/>
-      <c r="GB4" s="6"/>
-      <c r="GC4" s="6"/>
-      <c r="GD4" s="6"/>
-      <c r="GE4" s="6"/>
-      <c r="GF4" s="6"/>
-      <c r="GG4" s="6"/>
-      <c r="GH4" s="6"/>
-      <c r="GI4" s="6"/>
-      <c r="GJ4" s="6"/>
-      <c r="GK4" s="6"/>
-      <c r="GL4" s="6"/>
-      <c r="GM4" s="6"/>
-      <c r="GN4" s="6"/>
-      <c r="GO4" s="6"/>
-      <c r="GP4" s="6"/>
-      <c r="GQ4" s="6"/>
-      <c r="GR4" s="6"/>
-      <c r="GS4" s="6"/>
-      <c r="GT4" s="6"/>
-      <c r="GU4" s="6"/>
-      <c r="GV4" s="6"/>
-      <c r="GW4" s="6"/>
-      <c r="GX4" s="6"/>
-      <c r="GY4" s="6"/>
-      <c r="GZ4" s="6"/>
-      <c r="HA4" s="6"/>
-      <c r="HB4" s="6"/>
-      <c r="HC4" s="6"/>
-      <c r="HD4" s="6"/>
-      <c r="HE4" s="6"/>
-      <c r="HF4" s="6"/>
-      <c r="HG4" s="6"/>
-      <c r="HH4" s="6"/>
-      <c r="HI4" s="6"/>
-      <c r="HJ4" s="6"/>
-      <c r="HK4" s="6"/>
-      <c r="HL4" s="6"/>
-      <c r="HM4" s="6"/>
-      <c r="HN4" s="6"/>
-      <c r="HO4" s="6"/>
-      <c r="HP4" s="6"/>
-      <c r="HQ4" s="6"/>
-      <c r="HR4" s="6"/>
-      <c r="HS4" s="6"/>
-      <c r="HT4" s="6"/>
-      <c r="HU4" s="6"/>
-      <c r="HV4" s="6"/>
-      <c r="HW4" s="6"/>
-      <c r="HX4" s="6"/>
-      <c r="HY4" s="6"/>
-      <c r="HZ4" s="6"/>
-      <c r="IA4" s="6"/>
-      <c r="IB4" s="6"/>
-      <c r="IC4" s="6"/>
-      <c r="ID4" s="6"/>
-      <c r="IE4" s="6"/>
-      <c r="IF4" s="6"/>
-      <c r="IG4" s="6"/>
-      <c r="IH4" s="6"/>
-      <c r="II4" s="6"/>
-      <c r="IJ4" s="6"/>
-      <c r="IK4" s="6"/>
-      <c r="IL4" s="6"/>
-      <c r="IM4" s="6"/>
-      <c r="IN4" s="6"/>
-      <c r="IO4" s="6"/>
-      <c r="IP4" s="6"/>
-      <c r="IQ4" s="6"/>
-      <c r="IR4" s="6"/>
-      <c r="IS4" s="6"/>
-      <c r="IT4" s="6"/>
-      <c r="IU4" s="6"/>
-      <c r="IV4" s="6"/>
-      <c r="IW4" s="6"/>
-      <c r="IX4" s="6"/>
-      <c r="IY4" s="6"/>
-      <c r="IZ4" s="6"/>
-    </row>
-    <row r="5" spans="1:260" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="64" t="s">
+    </row>
+    <row r="5" spans="1:81" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67" t="s">
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67" t="s">
+      <c r="I5" s="68"/>
+      <c r="J5" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="66"/>
-      <c r="L5" s="67" t="s">
+      <c r="K5" s="68"/>
+      <c r="L5" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="66"/>
+      <c r="M5" s="68"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -2860,259 +2155,22 @@
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="6"/>
-      <c r="AL5" s="6"/>
-      <c r="AM5" s="6"/>
-      <c r="AN5" s="6"/>
-      <c r="AO5" s="6"/>
-      <c r="AP5" s="6"/>
-      <c r="AQ5" s="6"/>
-      <c r="AR5" s="6"/>
-      <c r="AS5" s="6"/>
-      <c r="AT5" s="6"/>
-      <c r="AU5" s="6"/>
-      <c r="AV5" s="6"/>
-      <c r="AW5" s="6"/>
-      <c r="AX5" s="6"/>
-      <c r="AY5" s="6"/>
-      <c r="AZ5" s="6"/>
-      <c r="BA5" s="6"/>
-      <c r="BB5" s="6"/>
-      <c r="BC5" s="6"/>
-      <c r="BD5" s="6"/>
-      <c r="BE5" s="6"/>
-      <c r="BF5" s="6"/>
-      <c r="BG5" s="6"/>
-      <c r="BH5" s="6"/>
-      <c r="BI5" s="6"/>
-      <c r="BJ5" s="6"/>
-      <c r="BK5" s="6"/>
-      <c r="BL5" s="6"/>
-      <c r="BM5" s="6"/>
-      <c r="BN5" s="6"/>
-      <c r="BO5" s="6"/>
-      <c r="BP5" s="6"/>
-      <c r="BQ5" s="6"/>
-      <c r="BR5" s="6"/>
-      <c r="BS5" s="6"/>
-      <c r="BT5" s="6"/>
-      <c r="BU5" s="6"/>
-      <c r="BV5" s="6"/>
-      <c r="BW5" s="6"/>
-      <c r="BX5" s="6"/>
-      <c r="BY5" s="6"/>
-      <c r="BZ5" s="6"/>
-      <c r="CA5" s="6"/>
-      <c r="CB5" s="6"/>
-      <c r="CC5" s="6"/>
-      <c r="CD5" s="6"/>
-      <c r="CE5" s="6"/>
-      <c r="CF5" s="6"/>
-      <c r="CG5" s="6"/>
-      <c r="CH5" s="6"/>
-      <c r="CI5" s="6"/>
-      <c r="CJ5" s="6"/>
-      <c r="CK5" s="6"/>
-      <c r="CL5" s="6"/>
-      <c r="CM5" s="6"/>
-      <c r="CN5" s="6"/>
-      <c r="CO5" s="6"/>
-      <c r="CP5" s="6"/>
-      <c r="CQ5" s="6"/>
-      <c r="CR5" s="6"/>
-      <c r="CS5" s="6"/>
-      <c r="CT5" s="6"/>
-      <c r="CU5" s="6"/>
-      <c r="CV5" s="6"/>
-      <c r="CW5" s="6"/>
-      <c r="CX5" s="6"/>
-      <c r="CY5" s="6"/>
-      <c r="CZ5" s="6"/>
-      <c r="DA5" s="6"/>
-      <c r="DB5" s="6"/>
-      <c r="DC5" s="6"/>
-      <c r="DD5" s="6"/>
-      <c r="DE5" s="6"/>
-      <c r="DF5" s="6"/>
-      <c r="DG5" s="6"/>
-      <c r="DH5" s="6"/>
-      <c r="DI5" s="6"/>
-      <c r="DJ5" s="6"/>
-      <c r="DK5" s="6"/>
-      <c r="DL5" s="6"/>
-      <c r="DM5" s="6"/>
-      <c r="DN5" s="6"/>
-      <c r="DO5" s="6"/>
-      <c r="DP5" s="6"/>
-      <c r="DQ5" s="6"/>
-      <c r="DR5" s="6"/>
-      <c r="DS5" s="6"/>
-      <c r="DT5" s="6"/>
-      <c r="DU5" s="6"/>
-      <c r="DV5" s="6"/>
-      <c r="DW5" s="6"/>
-      <c r="DX5" s="6"/>
-      <c r="DY5" s="6"/>
-      <c r="DZ5" s="6"/>
-      <c r="EA5" s="6"/>
-      <c r="EB5" s="6"/>
-      <c r="EC5" s="6"/>
-      <c r="ED5" s="6"/>
-      <c r="EE5" s="6"/>
-      <c r="EF5" s="6"/>
-      <c r="EG5" s="6"/>
-      <c r="EH5" s="6"/>
-      <c r="EI5" s="6"/>
-      <c r="EJ5" s="6"/>
-      <c r="EK5" s="6"/>
-      <c r="EL5" s="6"/>
-      <c r="EM5" s="6"/>
-      <c r="EN5" s="6"/>
-      <c r="EO5" s="6"/>
-      <c r="EP5" s="6"/>
-      <c r="EQ5" s="6"/>
-      <c r="ER5" s="6"/>
-      <c r="ES5" s="6"/>
-      <c r="ET5" s="6"/>
-      <c r="EU5" s="6"/>
-      <c r="EV5" s="6"/>
-      <c r="EW5" s="6"/>
-      <c r="EX5" s="6"/>
-      <c r="EY5" s="6"/>
-      <c r="EZ5" s="6"/>
-      <c r="FA5" s="6"/>
-      <c r="FB5" s="6"/>
-      <c r="FC5" s="6"/>
-      <c r="FD5" s="6"/>
-      <c r="FE5" s="6"/>
-      <c r="FF5" s="6"/>
-      <c r="FG5" s="6"/>
-      <c r="FH5" s="6"/>
-      <c r="FI5" s="6"/>
-      <c r="FJ5" s="6"/>
-      <c r="FK5" s="6"/>
-      <c r="FL5" s="6"/>
-      <c r="FM5" s="6"/>
-      <c r="FN5" s="6"/>
-      <c r="FO5" s="6"/>
-      <c r="FP5" s="6"/>
-      <c r="FQ5" s="6"/>
-      <c r="FR5" s="6"/>
-      <c r="FS5" s="6"/>
-      <c r="FT5" s="6"/>
-      <c r="FU5" s="6"/>
-      <c r="FV5" s="6"/>
-      <c r="FW5" s="6"/>
-      <c r="FX5" s="6"/>
-      <c r="FY5" s="6"/>
-      <c r="FZ5" s="6"/>
-      <c r="GA5" s="6"/>
-      <c r="GB5" s="6"/>
-      <c r="GC5" s="6"/>
-      <c r="GD5" s="6"/>
-      <c r="GE5" s="6"/>
-      <c r="GF5" s="6"/>
-      <c r="GG5" s="6"/>
-      <c r="GH5" s="6"/>
-      <c r="GI5" s="6"/>
-      <c r="GJ5" s="6"/>
-      <c r="GK5" s="6"/>
-      <c r="GL5" s="6"/>
-      <c r="GM5" s="6"/>
-      <c r="GN5" s="6"/>
-      <c r="GO5" s="6"/>
-      <c r="GP5" s="6"/>
-      <c r="GQ5" s="6"/>
-      <c r="GR5" s="6"/>
-      <c r="GS5" s="6"/>
-      <c r="GT5" s="6"/>
-      <c r="GU5" s="6"/>
-      <c r="GV5" s="6"/>
-      <c r="GW5" s="6"/>
-      <c r="GX5" s="6"/>
-      <c r="GY5" s="6"/>
-      <c r="GZ5" s="6"/>
-      <c r="HA5" s="6"/>
-      <c r="HB5" s="6"/>
-      <c r="HC5" s="6"/>
-      <c r="HD5" s="6"/>
-      <c r="HE5" s="6"/>
-      <c r="HF5" s="6"/>
-      <c r="HG5" s="6"/>
-      <c r="HH5" s="6"/>
-      <c r="HI5" s="6"/>
-      <c r="HJ5" s="6"/>
-      <c r="HK5" s="6"/>
-      <c r="HL5" s="6"/>
-      <c r="HM5" s="6"/>
-      <c r="HN5" s="6"/>
-      <c r="HO5" s="6"/>
-      <c r="HP5" s="6"/>
-      <c r="HQ5" s="6"/>
-      <c r="HR5" s="6"/>
-      <c r="HS5" s="6"/>
-      <c r="HT5" s="6"/>
-      <c r="HU5" s="6"/>
-      <c r="HV5" s="6"/>
-      <c r="HW5" s="6"/>
-      <c r="HX5" s="6"/>
-      <c r="HY5" s="6"/>
-      <c r="HZ5" s="6"/>
-      <c r="IA5" s="6"/>
-      <c r="IB5" s="6"/>
-      <c r="IC5" s="6"/>
-      <c r="ID5" s="6"/>
-      <c r="IE5" s="6"/>
-      <c r="IF5" s="6"/>
-      <c r="IG5" s="6"/>
-      <c r="IH5" s="6"/>
-      <c r="II5" s="6"/>
-      <c r="IJ5" s="6"/>
-      <c r="IK5" s="6"/>
-      <c r="IL5" s="6"/>
-      <c r="IM5" s="6"/>
-      <c r="IN5" s="6"/>
-      <c r="IO5" s="6"/>
-      <c r="IP5" s="6"/>
-      <c r="IQ5" s="6"/>
-      <c r="IR5" s="6"/>
-      <c r="IS5" s="6"/>
-      <c r="IT5" s="6"/>
-      <c r="IU5" s="6"/>
-      <c r="IV5" s="6"/>
-      <c r="IW5" s="6"/>
-      <c r="IX5" s="6"/>
-      <c r="IY5" s="6"/>
-      <c r="IZ5" s="6"/>
-    </row>
-    <row r="6" spans="1:260" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="69"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="78" t="s">
+    </row>
+    <row r="6" spans="1:81" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="71"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="71"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="73"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -3123,746 +2181,53 @@
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
-      <c r="AO6" s="6"/>
-      <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
-      <c r="AS6" s="6"/>
-      <c r="AT6" s="6"/>
-      <c r="AU6" s="6"/>
-      <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AX6" s="6"/>
-      <c r="AY6" s="6"/>
-      <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
-      <c r="BF6" s="6"/>
-      <c r="BG6" s="6"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
-      <c r="BM6" s="6"/>
-      <c r="BN6" s="6"/>
-      <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6"/>
-      <c r="BT6" s="6"/>
-      <c r="BU6" s="6"/>
-      <c r="BV6" s="6"/>
-      <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
-      <c r="BZ6" s="6"/>
-      <c r="CA6" s="6"/>
-      <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6"/>
-      <c r="CF6" s="6"/>
-      <c r="CG6" s="6"/>
-      <c r="CH6" s="6"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="6"/>
-      <c r="CK6" s="6"/>
-      <c r="CL6" s="6"/>
-      <c r="CM6" s="6"/>
-      <c r="CN6" s="6"/>
-      <c r="CO6" s="6"/>
-      <c r="CP6" s="6"/>
-      <c r="CQ6" s="6"/>
-      <c r="CR6" s="6"/>
-      <c r="CS6" s="6"/>
-      <c r="CT6" s="6"/>
-      <c r="CU6" s="6"/>
-      <c r="CV6" s="6"/>
-      <c r="CW6" s="6"/>
-      <c r="CX6" s="6"/>
-      <c r="CY6" s="6"/>
-      <c r="CZ6" s="6"/>
-      <c r="DA6" s="6"/>
-      <c r="DB6" s="6"/>
-      <c r="DC6" s="6"/>
-      <c r="DD6" s="6"/>
-      <c r="DE6" s="6"/>
-      <c r="DF6" s="6"/>
-      <c r="DG6" s="6"/>
-      <c r="DH6" s="6"/>
-      <c r="DI6" s="6"/>
-      <c r="DJ6" s="6"/>
-      <c r="DK6" s="6"/>
-      <c r="DL6" s="6"/>
-      <c r="DM6" s="6"/>
-      <c r="DN6" s="6"/>
-      <c r="DO6" s="6"/>
-      <c r="DP6" s="6"/>
-      <c r="DQ6" s="6"/>
-      <c r="DR6" s="6"/>
-      <c r="DS6" s="6"/>
-      <c r="DT6" s="6"/>
-      <c r="DU6" s="6"/>
-      <c r="DV6" s="6"/>
-      <c r="DW6" s="6"/>
-      <c r="DX6" s="6"/>
-      <c r="DY6" s="6"/>
-      <c r="DZ6" s="6"/>
-      <c r="EA6" s="6"/>
-      <c r="EB6" s="6"/>
-      <c r="EC6" s="6"/>
-      <c r="ED6" s="6"/>
-      <c r="EE6" s="6"/>
-      <c r="EF6" s="6"/>
-      <c r="EG6" s="6"/>
-      <c r="EH6" s="6"/>
-      <c r="EI6" s="6"/>
-      <c r="EJ6" s="6"/>
-      <c r="EK6" s="6"/>
-      <c r="EL6" s="6"/>
-      <c r="EM6" s="6"/>
-      <c r="EN6" s="6"/>
-      <c r="EO6" s="6"/>
-      <c r="EP6" s="6"/>
-      <c r="EQ6" s="6"/>
-      <c r="ER6" s="6"/>
-      <c r="ES6" s="6"/>
-      <c r="ET6" s="6"/>
-      <c r="EU6" s="6"/>
-      <c r="EV6" s="6"/>
-      <c r="EW6" s="6"/>
-      <c r="EX6" s="6"/>
-      <c r="EY6" s="6"/>
-      <c r="EZ6" s="6"/>
-      <c r="FA6" s="6"/>
-      <c r="FB6" s="6"/>
-      <c r="FC6" s="6"/>
-      <c r="FD6" s="6"/>
-      <c r="FE6" s="6"/>
-      <c r="FF6" s="6"/>
-      <c r="FG6" s="6"/>
-      <c r="FH6" s="6"/>
-      <c r="FI6" s="6"/>
-      <c r="FJ6" s="6"/>
-      <c r="FK6" s="6"/>
-      <c r="FL6" s="6"/>
-      <c r="FM6" s="6"/>
-      <c r="FN6" s="6"/>
-      <c r="FO6" s="6"/>
-      <c r="FP6" s="6"/>
-      <c r="FQ6" s="6"/>
-      <c r="FR6" s="6"/>
-      <c r="FS6" s="6"/>
-      <c r="FT6" s="6"/>
-      <c r="FU6" s="6"/>
-      <c r="FV6" s="6"/>
-      <c r="FW6" s="6"/>
-      <c r="FX6" s="6"/>
-      <c r="FY6" s="6"/>
-      <c r="FZ6" s="6"/>
-      <c r="GA6" s="6"/>
-      <c r="GB6" s="6"/>
-      <c r="GC6" s="6"/>
-      <c r="GD6" s="6"/>
-      <c r="GE6" s="6"/>
-      <c r="GF6" s="6"/>
-      <c r="GG6" s="6"/>
-      <c r="GH6" s="6"/>
-      <c r="GI6" s="6"/>
-      <c r="GJ6" s="6"/>
-      <c r="GK6" s="6"/>
-      <c r="GL6" s="6"/>
-      <c r="GM6" s="6"/>
-      <c r="GN6" s="6"/>
-      <c r="GO6" s="6"/>
-      <c r="GP6" s="6"/>
-      <c r="GQ6" s="6"/>
-      <c r="GR6" s="6"/>
-      <c r="GS6" s="6"/>
-      <c r="GT6" s="6"/>
-      <c r="GU6" s="6"/>
-      <c r="GV6" s="6"/>
-      <c r="GW6" s="6"/>
-      <c r="GX6" s="6"/>
-      <c r="GY6" s="6"/>
-      <c r="GZ6" s="6"/>
-      <c r="HA6" s="6"/>
-      <c r="HB6" s="6"/>
-      <c r="HC6" s="6"/>
-      <c r="HD6" s="6"/>
-      <c r="HE6" s="6"/>
-      <c r="HF6" s="6"/>
-      <c r="HG6" s="6"/>
-      <c r="HH6" s="6"/>
-      <c r="HI6" s="6"/>
-      <c r="HJ6" s="6"/>
-      <c r="HK6" s="6"/>
-      <c r="HL6" s="6"/>
-      <c r="HM6" s="6"/>
-      <c r="HN6" s="6"/>
-      <c r="HO6" s="6"/>
-      <c r="HP6" s="6"/>
-      <c r="HQ6" s="6"/>
-      <c r="HR6" s="6"/>
-      <c r="HS6" s="6"/>
-      <c r="HT6" s="6"/>
-      <c r="HU6" s="6"/>
-      <c r="HV6" s="6"/>
-      <c r="HW6" s="6"/>
-      <c r="HX6" s="6"/>
-      <c r="HY6" s="6"/>
-      <c r="HZ6" s="6"/>
-      <c r="IA6" s="6"/>
-      <c r="IB6" s="6"/>
-      <c r="IC6" s="6"/>
-      <c r="ID6" s="6"/>
-      <c r="IE6" s="6"/>
-      <c r="IF6" s="6"/>
-      <c r="IG6" s="6"/>
-      <c r="IH6" s="6"/>
-      <c r="II6" s="6"/>
-      <c r="IJ6" s="6"/>
-      <c r="IK6" s="6"/>
-      <c r="IL6" s="6"/>
-      <c r="IM6" s="6"/>
-      <c r="IN6" s="6"/>
-      <c r="IO6" s="6"/>
-      <c r="IP6" s="6"/>
-      <c r="IQ6" s="6"/>
-      <c r="IR6" s="6"/>
-      <c r="IS6" s="6"/>
-      <c r="IT6" s="6"/>
-      <c r="IU6" s="6"/>
-      <c r="IV6" s="6"/>
-      <c r="IW6" s="6"/>
-      <c r="IX6" s="6"/>
-      <c r="IY6" s="6"/>
-      <c r="IZ6" s="6"/>
-    </row>
-    <row r="7" spans="1:260" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="74" t="s">
+    </row>
+    <row r="7" spans="1:81" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="76"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="78"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="6"/>
-      <c r="AM7" s="6"/>
-      <c r="AN7" s="6"/>
-      <c r="AO7" s="6"/>
-      <c r="AP7" s="6"/>
-      <c r="AQ7" s="6"/>
-      <c r="AR7" s="6"/>
-      <c r="AS7" s="6"/>
-      <c r="AT7" s="6"/>
-      <c r="AU7" s="6"/>
-      <c r="AV7" s="6"/>
-      <c r="AW7" s="6"/>
-      <c r="AX7" s="6"/>
-      <c r="AY7" s="6"/>
-      <c r="AZ7" s="6"/>
-      <c r="BA7" s="6"/>
-      <c r="BB7" s="6"/>
-      <c r="BC7" s="6"/>
-      <c r="BD7" s="6"/>
-      <c r="BE7" s="6"/>
-      <c r="BF7" s="6"/>
-      <c r="BG7" s="6"/>
-      <c r="BH7" s="6"/>
-      <c r="BI7" s="6"/>
-      <c r="BJ7" s="6"/>
-      <c r="BK7" s="6"/>
-      <c r="BL7" s="6"/>
-      <c r="BM7" s="6"/>
-      <c r="BN7" s="6"/>
-      <c r="BO7" s="6"/>
-      <c r="BP7" s="6"/>
-      <c r="BQ7" s="6"/>
-      <c r="BR7" s="6"/>
-      <c r="BS7" s="6"/>
-      <c r="BT7" s="6"/>
-      <c r="BU7" s="6"/>
-      <c r="BV7" s="6"/>
-      <c r="BW7" s="6"/>
-      <c r="BX7" s="6"/>
-      <c r="BY7" s="6"/>
-      <c r="BZ7" s="6"/>
-      <c r="CA7" s="6"/>
-      <c r="CB7" s="6"/>
-      <c r="CC7" s="6"/>
-      <c r="CD7" s="6"/>
-      <c r="CE7" s="6"/>
-      <c r="CF7" s="6"/>
-      <c r="CG7" s="6"/>
-      <c r="CH7" s="6"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="6"/>
-      <c r="CK7" s="6"/>
-      <c r="CL7" s="6"/>
-      <c r="CM7" s="6"/>
-      <c r="CN7" s="6"/>
-      <c r="CO7" s="6"/>
-      <c r="CP7" s="6"/>
-      <c r="CQ7" s="6"/>
-      <c r="CR7" s="6"/>
-      <c r="CS7" s="6"/>
-      <c r="CT7" s="6"/>
-      <c r="CU7" s="6"/>
-      <c r="CV7" s="6"/>
-      <c r="CW7" s="6"/>
-      <c r="CX7" s="6"/>
-      <c r="CY7" s="6"/>
-      <c r="CZ7" s="6"/>
-      <c r="DA7" s="6"/>
-      <c r="DB7" s="6"/>
-      <c r="DC7" s="6"/>
-      <c r="DD7" s="6"/>
-      <c r="DE7" s="6"/>
-      <c r="DF7" s="6"/>
-      <c r="DG7" s="6"/>
-      <c r="DH7" s="6"/>
-      <c r="DI7" s="6"/>
-      <c r="DJ7" s="6"/>
-      <c r="DK7" s="6"/>
-      <c r="DL7" s="6"/>
-      <c r="DM7" s="6"/>
-      <c r="DN7" s="6"/>
-      <c r="DO7" s="6"/>
-      <c r="DP7" s="6"/>
-      <c r="DQ7" s="6"/>
-      <c r="DR7" s="6"/>
-      <c r="DS7" s="6"/>
-      <c r="DT7" s="6"/>
-      <c r="DU7" s="6"/>
-      <c r="DV7" s="6"/>
-      <c r="DW7" s="6"/>
-      <c r="DX7" s="6"/>
-      <c r="DY7" s="6"/>
-      <c r="DZ7" s="6"/>
-      <c r="EA7" s="6"/>
-      <c r="EB7" s="6"/>
-      <c r="EC7" s="6"/>
-      <c r="ED7" s="6"/>
-      <c r="EE7" s="6"/>
-      <c r="EF7" s="6"/>
-      <c r="EG7" s="6"/>
-      <c r="EH7" s="6"/>
-      <c r="EI7" s="6"/>
-      <c r="EJ7" s="6"/>
-      <c r="EK7" s="6"/>
-      <c r="EL7" s="6"/>
-      <c r="EM7" s="6"/>
-      <c r="EN7" s="6"/>
-      <c r="EO7" s="6"/>
-      <c r="EP7" s="6"/>
-      <c r="EQ7" s="6"/>
-      <c r="ER7" s="6"/>
-      <c r="ES7" s="6"/>
-      <c r="ET7" s="6"/>
-      <c r="EU7" s="6"/>
-      <c r="EV7" s="6"/>
-      <c r="EW7" s="6"/>
-      <c r="EX7" s="6"/>
-      <c r="EY7" s="6"/>
-      <c r="EZ7" s="6"/>
-      <c r="FA7" s="6"/>
-      <c r="FB7" s="6"/>
-      <c r="FC7" s="6"/>
-      <c r="FD7" s="6"/>
-      <c r="FE7" s="6"/>
-      <c r="FF7" s="6"/>
-      <c r="FG7" s="6"/>
-      <c r="FH7" s="6"/>
-      <c r="FI7" s="6"/>
-      <c r="FJ7" s="6"/>
-      <c r="FK7" s="6"/>
-      <c r="FL7" s="6"/>
-      <c r="FM7" s="6"/>
-      <c r="FN7" s="6"/>
-      <c r="FO7" s="6"/>
-      <c r="FP7" s="6"/>
-      <c r="FQ7" s="6"/>
-      <c r="FR7" s="6"/>
-      <c r="FS7" s="6"/>
-      <c r="FT7" s="6"/>
-      <c r="FU7" s="6"/>
-      <c r="FV7" s="6"/>
-      <c r="FW7" s="6"/>
-      <c r="FX7" s="6"/>
-      <c r="FY7" s="6"/>
-      <c r="FZ7" s="6"/>
-      <c r="GA7" s="6"/>
-      <c r="GB7" s="6"/>
-      <c r="GC7" s="6"/>
-      <c r="GD7" s="6"/>
-      <c r="GE7" s="6"/>
-      <c r="GF7" s="6"/>
-      <c r="GG7" s="6"/>
-      <c r="GH7" s="6"/>
-      <c r="GI7" s="6"/>
-      <c r="GJ7" s="6"/>
-      <c r="GK7" s="6"/>
-      <c r="GL7" s="6"/>
-      <c r="GM7" s="6"/>
-      <c r="GN7" s="6"/>
-      <c r="GO7" s="6"/>
-      <c r="GP7" s="6"/>
-      <c r="GQ7" s="6"/>
-      <c r="GR7" s="6"/>
-      <c r="GS7" s="6"/>
-      <c r="GT7" s="6"/>
-      <c r="GU7" s="6"/>
-      <c r="GV7" s="6"/>
-      <c r="GW7" s="6"/>
-      <c r="GX7" s="6"/>
-      <c r="GY7" s="6"/>
-      <c r="GZ7" s="6"/>
-      <c r="HA7" s="6"/>
-      <c r="HB7" s="6"/>
-      <c r="HC7" s="6"/>
-      <c r="HD7" s="6"/>
-      <c r="HE7" s="6"/>
-      <c r="HF7" s="6"/>
-      <c r="HG7" s="6"/>
-      <c r="HH7" s="6"/>
-      <c r="HI7" s="6"/>
-      <c r="HJ7" s="6"/>
-      <c r="HK7" s="6"/>
-      <c r="HL7" s="6"/>
-      <c r="HM7" s="6"/>
-      <c r="HN7" s="6"/>
-      <c r="HO7" s="6"/>
-      <c r="HP7" s="6"/>
-      <c r="HQ7" s="6"/>
-      <c r="HR7" s="6"/>
-      <c r="HS7" s="6"/>
-      <c r="HT7" s="6"/>
-      <c r="HU7" s="6"/>
-      <c r="HV7" s="6"/>
-      <c r="HW7" s="6"/>
-      <c r="HX7" s="6"/>
-      <c r="HY7" s="6"/>
-      <c r="HZ7" s="6"/>
-      <c r="IA7" s="6"/>
-      <c r="IB7" s="6"/>
-      <c r="IC7" s="6"/>
-      <c r="ID7" s="6"/>
-      <c r="IE7" s="6"/>
-      <c r="IF7" s="6"/>
-      <c r="IG7" s="6"/>
-      <c r="IH7" s="6"/>
-      <c r="II7" s="6"/>
-      <c r="IJ7" s="6"/>
-      <c r="IK7" s="6"/>
-      <c r="IL7" s="6"/>
-      <c r="IM7" s="6"/>
-      <c r="IN7" s="6"/>
-      <c r="IO7" s="6"/>
-      <c r="IP7" s="6"/>
-      <c r="IQ7" s="6"/>
-    </row>
-    <row r="8" spans="1:260" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="77" t="s">
+    </row>
+    <row r="8" spans="1:81" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="79" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="71"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="73"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="6"/>
-      <c r="AM8" s="6"/>
-      <c r="AN8" s="6"/>
-      <c r="AO8" s="6"/>
-      <c r="AP8" s="6"/>
-      <c r="AQ8" s="6"/>
-      <c r="AR8" s="6"/>
-      <c r="AS8" s="6"/>
-      <c r="AT8" s="6"/>
-      <c r="AU8" s="6"/>
-      <c r="AV8" s="6"/>
-      <c r="AW8" s="6"/>
-      <c r="AX8" s="6"/>
-      <c r="AY8" s="6"/>
-      <c r="AZ8" s="6"/>
-      <c r="BA8" s="6"/>
-      <c r="BB8" s="6"/>
-      <c r="BC8" s="6"/>
-      <c r="BD8" s="6"/>
-      <c r="BE8" s="6"/>
-      <c r="BF8" s="6"/>
-      <c r="BG8" s="6"/>
-      <c r="BH8" s="6"/>
-      <c r="BI8" s="6"/>
-      <c r="BJ8" s="6"/>
-      <c r="BK8" s="6"/>
-      <c r="BL8" s="6"/>
-      <c r="BM8" s="6"/>
-      <c r="BN8" s="6"/>
-      <c r="BO8" s="6"/>
-      <c r="BP8" s="6"/>
-      <c r="BQ8" s="6"/>
-      <c r="BR8" s="6"/>
-      <c r="BS8" s="6"/>
-      <c r="BT8" s="6"/>
-      <c r="BU8" s="6"/>
-      <c r="BV8" s="6"/>
-      <c r="BW8" s="6"/>
-      <c r="BX8" s="6"/>
-      <c r="BY8" s="6"/>
-      <c r="BZ8" s="6"/>
-      <c r="CA8" s="6"/>
-      <c r="CB8" s="6"/>
-      <c r="CC8" s="6"/>
-      <c r="CD8" s="6"/>
-      <c r="CE8" s="6"/>
-      <c r="CF8" s="6"/>
-      <c r="CG8" s="6"/>
-      <c r="CH8" s="6"/>
-      <c r="CI8" s="6"/>
-      <c r="CJ8" s="6"/>
-      <c r="CK8" s="6"/>
-      <c r="CL8" s="6"/>
-      <c r="CM8" s="6"/>
-      <c r="CN8" s="6"/>
-      <c r="CO8" s="6"/>
-      <c r="CP8" s="6"/>
-      <c r="CQ8" s="6"/>
-      <c r="CR8" s="6"/>
-      <c r="CS8" s="6"/>
-      <c r="CT8" s="6"/>
-      <c r="CU8" s="6"/>
-      <c r="CV8" s="6"/>
-      <c r="CW8" s="6"/>
-      <c r="CX8" s="6"/>
-      <c r="CY8" s="6"/>
-      <c r="CZ8" s="6"/>
-      <c r="DA8" s="6"/>
-      <c r="DB8" s="6"/>
-      <c r="DC8" s="6"/>
-      <c r="DD8" s="6"/>
-      <c r="DE8" s="6"/>
-      <c r="DF8" s="6"/>
-      <c r="DG8" s="6"/>
-      <c r="DH8" s="6"/>
-      <c r="DI8" s="6"/>
-      <c r="DJ8" s="6"/>
-      <c r="DK8" s="6"/>
-      <c r="DL8" s="6"/>
-      <c r="DM8" s="6"/>
-      <c r="DN8" s="6"/>
-      <c r="DO8" s="6"/>
-      <c r="DP8" s="6"/>
-      <c r="DQ8" s="6"/>
-      <c r="DR8" s="6"/>
-      <c r="DS8" s="6"/>
-      <c r="DT8" s="6"/>
-      <c r="DU8" s="6"/>
-      <c r="DV8" s="6"/>
-      <c r="DW8" s="6"/>
-      <c r="DX8" s="6"/>
-      <c r="DY8" s="6"/>
-      <c r="DZ8" s="6"/>
-      <c r="EA8" s="6"/>
-      <c r="EB8" s="6"/>
-      <c r="EC8" s="6"/>
-      <c r="ED8" s="6"/>
-      <c r="EE8" s="6"/>
-      <c r="EF8" s="6"/>
-      <c r="EG8" s="6"/>
-      <c r="EH8" s="6"/>
-      <c r="EI8" s="6"/>
-      <c r="EJ8" s="6"/>
-      <c r="EK8" s="6"/>
-      <c r="EL8" s="6"/>
-      <c r="EM8" s="6"/>
-      <c r="EN8" s="6"/>
-      <c r="EO8" s="6"/>
-      <c r="EP8" s="6"/>
-      <c r="EQ8" s="6"/>
-      <c r="ER8" s="6"/>
-      <c r="ES8" s="6"/>
-      <c r="ET8" s="6"/>
-      <c r="EU8" s="6"/>
-      <c r="EV8" s="6"/>
-      <c r="EW8" s="6"/>
-      <c r="EX8" s="6"/>
-      <c r="EY8" s="6"/>
-      <c r="EZ8" s="6"/>
-      <c r="FA8" s="6"/>
-      <c r="FB8" s="6"/>
-      <c r="FC8" s="6"/>
-      <c r="FD8" s="6"/>
-      <c r="FE8" s="6"/>
-      <c r="FF8" s="6"/>
-      <c r="FG8" s="6"/>
-      <c r="FH8" s="6"/>
-      <c r="FI8" s="6"/>
-      <c r="FJ8" s="6"/>
-      <c r="FK8" s="6"/>
-      <c r="FL8" s="6"/>
-      <c r="FM8" s="6"/>
-      <c r="FN8" s="6"/>
-      <c r="FO8" s="6"/>
-      <c r="FP8" s="6"/>
-      <c r="FQ8" s="6"/>
-      <c r="FR8" s="6"/>
-      <c r="FS8" s="6"/>
-      <c r="FT8" s="6"/>
-      <c r="FU8" s="6"/>
-      <c r="FV8" s="6"/>
-      <c r="FW8" s="6"/>
-      <c r="FX8" s="6"/>
-      <c r="FY8" s="6"/>
-      <c r="FZ8" s="6"/>
-      <c r="GA8" s="6"/>
-      <c r="GB8" s="6"/>
-      <c r="GC8" s="6"/>
-      <c r="GD8" s="6"/>
-      <c r="GE8" s="6"/>
-      <c r="GF8" s="6"/>
-      <c r="GG8" s="6"/>
-      <c r="GH8" s="6"/>
-      <c r="GI8" s="6"/>
-      <c r="GJ8" s="6"/>
-      <c r="GK8" s="6"/>
-      <c r="GL8" s="6"/>
-      <c r="GM8" s="6"/>
-      <c r="GN8" s="6"/>
-      <c r="GO8" s="6"/>
-      <c r="GP8" s="6"/>
-      <c r="GQ8" s="6"/>
-      <c r="GR8" s="6"/>
-      <c r="GS8" s="6"/>
-      <c r="GT8" s="6"/>
-      <c r="GU8" s="6"/>
-      <c r="GV8" s="6"/>
-      <c r="GW8" s="6"/>
-      <c r="GX8" s="6"/>
-      <c r="GY8" s="6"/>
-      <c r="GZ8" s="6"/>
-      <c r="HA8" s="6"/>
-      <c r="HB8" s="6"/>
-      <c r="HC8" s="6"/>
-      <c r="HD8" s="6"/>
-      <c r="HE8" s="6"/>
-      <c r="HF8" s="6"/>
-      <c r="HG8" s="6"/>
-      <c r="HH8" s="6"/>
-      <c r="HI8" s="6"/>
-      <c r="HJ8" s="6"/>
-      <c r="HK8" s="6"/>
-      <c r="HL8" s="6"/>
-      <c r="HM8" s="6"/>
-      <c r="HN8" s="6"/>
-      <c r="HO8" s="6"/>
-      <c r="HP8" s="6"/>
-      <c r="HQ8" s="6"/>
-      <c r="HR8" s="6"/>
-      <c r="HS8" s="6"/>
-      <c r="HT8" s="6"/>
-      <c r="HU8" s="6"/>
-      <c r="HV8" s="6"/>
-      <c r="HW8" s="6"/>
-      <c r="HX8" s="6"/>
-      <c r="HY8" s="6"/>
-      <c r="HZ8" s="6"/>
-      <c r="IA8" s="6"/>
-      <c r="IB8" s="6"/>
-      <c r="IC8" s="6"/>
-      <c r="ID8" s="6"/>
-      <c r="IE8" s="6"/>
-      <c r="IF8" s="6"/>
-      <c r="IG8" s="6"/>
-      <c r="IH8" s="6"/>
-      <c r="II8" s="6"/>
-      <c r="IJ8" s="6"/>
-      <c r="IK8" s="6"/>
-      <c r="IL8" s="6"/>
-      <c r="IM8" s="6"/>
-      <c r="IN8" s="6"/>
-      <c r="IO8" s="6"/>
-      <c r="IP8" s="6"/>
-      <c r="IQ8" s="6"/>
-    </row>
-    <row r="9" spans="1:260" s="7" customFormat="1" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:260" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:81" s="7" customFormat="1" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:81" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="21" t="s">
         <v>10</v>
       </c>
@@ -3877,22 +2242,22 @@
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="54" t="s">
+      <c r="N10" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="57" t="s">
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="59"/>
-    </row>
-    <row r="11" spans="1:260" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="61"/>
+    </row>
+    <row r="11" spans="1:81" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="24" t="s">
         <v>13</v>
       </c>
@@ -3911,20 +2276,20 @@
       <c r="G11" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="62" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="60" t="s">
+      <c r="L11" s="65"/>
+      <c r="M11" s="62" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="27" t="s">
@@ -3945,20 +2310,20 @@
       <c r="S11" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="T11" s="60" t="s">
+      <c r="T11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="U11" s="60" t="s">
+      <c r="U11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="V11" s="60" t="s">
+      <c r="V11" s="62" t="s">
         <v>22</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:260" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:81" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
@@ -3977,18 +2342,18 @@
       <c r="G12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="61"/>
+      <c r="H12" s="63"/>
       <c r="I12" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="61"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="26" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="61"/>
+      <c r="M12" s="63"/>
       <c r="N12" s="17" t="s">
         <v>35</v>
       </c>
@@ -4007,14 +2372,14 @@
       <c r="S12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="T12" s="61"/>
-      <c r="U12" s="61"/>
-      <c r="V12" s="61"/>
+      <c r="T12" s="63"/>
+      <c r="U12" s="63"/>
+      <c r="V12" s="63"/>
       <c r="W12" s="20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:260" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:81" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>1</v>
       </c>
@@ -4074,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:260" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:81" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>2</v>
       </c>
@@ -4134,7 +2499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:260" s="1" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:81" s="1" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>3</v>
       </c>
@@ -4194,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:260" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:81" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>4</v>
       </c>
@@ -4481,7 +2846,7 @@
       <c r="P20" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="Q20" s="80" t="s">
+      <c r="Q20" s="55" t="s">
         <v>170</v>
       </c>
       <c r="R20" s="15"/>
@@ -4739,7 +3104,7 @@
       </c>
     </row>
     <row r="26" spans="2:23" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="79" t="s">
+      <c r="D26" s="54" t="s">
         <v>121</v>
       </c>
     </row>
@@ -4800,7 +3165,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0" footer="0"/>
-  <pageSetup scale="83" fitToWidth="2" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
